--- a/Selenium/Automation_Testing_Insider/Full_Selenium_Framework/src/test/resources/TestData/TestData.xlsx
+++ b/Selenium/Automation_Testing_Insider/Full_Selenium_Framework/src/test/resources/TestData/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LearningAutomation\Selenium\Automation_Testing_Insider\Full_Selenium_Framework\src\test\resources\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3738E0E0-4F61-48A9-95CD-D054DDEA786C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F9AA55D-9BAF-4432-9BD7-6473BFDAD104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8145" yWindow="2520" windowWidth="14460" windowHeight="11295" activeTab="1" xr2:uid="{474F8DD2-0D31-4D57-93FB-7ECD0C04FCA0}"/>
+    <workbookView xWindow="6600" yWindow="1470" windowWidth="14460" windowHeight="11295" xr2:uid="{474F8DD2-0D31-4D57-93FB-7ECD0C04FCA0}"/>
   </bookViews>
   <sheets>
     <sheet name="ValidLoginData" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
   <si>
     <t>username</t>
   </si>
@@ -51,10 +51,13 @@
     <t>password</t>
   </si>
   <si>
-    <t>admin123</t>
-  </si>
-  <si>
     <t>admin12</t>
+  </si>
+  <si>
+    <t>test_gupta</t>
+  </si>
+  <si>
+    <t>Stupid1!Password</t>
   </si>
 </sst>
 </file>
@@ -439,10 +442,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -468,7 +471,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Selenium/Automation_Testing_Insider/Full_Selenium_Framework/src/test/resources/TestData/TestData.xlsx
+++ b/Selenium/Automation_Testing_Insider/Full_Selenium_Framework/src/test/resources/TestData/TestData.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LearningAutomation\Selenium\Automation_Testing_Insider\Full_Selenium_Framework\src\test\resources\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F9AA55D-9BAF-4432-9BD7-6473BFDAD104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D03707F-9ED5-49FC-8012-F35D40712A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6600" yWindow="1470" windowWidth="14460" windowHeight="11295" xr2:uid="{474F8DD2-0D31-4D57-93FB-7ECD0C04FCA0}"/>
+    <workbookView xWindow="6600" yWindow="1470" windowWidth="14460" windowHeight="11295" activeTab="1" xr2:uid="{474F8DD2-0D31-4D57-93FB-7ECD0C04FCA0}"/>
   </bookViews>
   <sheets>
     <sheet name="ValidLoginData" sheetId="1" r:id="rId1"/>
-    <sheet name="InvalidLoginData" sheetId="2" r:id="rId2"/>
+    <sheet name="EmployeeVerification" sheetId="3" r:id="rId2"/>
+    <sheet name="InvalidLoginData" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>username</t>
   </si>
@@ -58,6 +59,18 @@
   </si>
   <si>
     <t>Stupid1!Password</t>
+  </si>
+  <si>
+    <t>emp_id</t>
+  </si>
+  <si>
+    <t>emp_name</t>
+  </si>
+  <si>
+    <t>Ingrid</t>
+  </si>
+  <si>
+    <t>Samir</t>
   </si>
 </sst>
 </file>
@@ -454,6 +467,40 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFD21EF7-3CE0-4B86-91D2-7779F43F692D}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C51630B-FD18-4CA9-A37F-58F2CA711C37}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
